--- a/reports/二级子公司D_利润表_2025-05.xlsx
+++ b/reports/二级子公司D_利润表_2025-05.xlsx
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="F3" s="13" t="n">
-        <v>85188221</v>
+        <v>87829136</v>
       </c>
       <c r="G3" s="13" t="n"/>
       <c r="I3" s="5" t="n"/>
@@ -2081,10 +2081,10 @@
         </is>
       </c>
       <c r="F4" s="14" t="n">
-        <v>83288881</v>
+        <v>84096031</v>
       </c>
       <c r="G4" s="14" t="n">
-        <v>388607406</v>
+        <v>388770102</v>
       </c>
       <c r="I4" s="5" t="n"/>
     </row>
@@ -2115,10 +2115,10 @@
         </is>
       </c>
       <c r="F5" s="14" t="n">
-        <v>287773</v>
+        <v>288587</v>
       </c>
       <c r="G5" s="14" t="n">
-        <v>1340617</v>
+        <v>1344580</v>
       </c>
     </row>
     <row r="6" ht="18" customHeight="1">
@@ -2148,10 +2148,10 @@
         </is>
       </c>
       <c r="F6" s="14" t="n">
-        <v>248166</v>
+        <v>246742</v>
       </c>
       <c r="G6" s="14" t="n">
-        <v>1150535</v>
+        <v>1152379</v>
       </c>
     </row>
     <row r="7" ht="18" customHeight="1">
@@ -2181,10 +2181,10 @@
         </is>
       </c>
       <c r="F7" s="14" t="n">
-        <v>204930</v>
+        <v>205170</v>
       </c>
       <c r="G7" s="14" t="n">
-        <v>956947</v>
+        <v>959808</v>
       </c>
     </row>
     <row r="8" ht="18" customHeight="1">
@@ -2214,10 +2214,10 @@
         </is>
       </c>
       <c r="F8" s="14" t="n">
-        <v>186493</v>
+        <v>184380</v>
       </c>
       <c r="G8" s="14" t="n">
-        <v>863287</v>
+        <v>863084</v>
       </c>
     </row>
     <row r="9" ht="18" customHeight="1">
@@ -2247,10 +2247,10 @@
         </is>
       </c>
       <c r="F9" s="14" t="n">
-        <v>102389</v>
+        <v>102382</v>
       </c>
       <c r="G9" s="14" t="n">
-        <v>478386</v>
+        <v>478993</v>
       </c>
     </row>
     <row r="10" ht="18" customHeight="1">
@@ -2280,10 +2280,10 @@
         </is>
       </c>
       <c r="F10" s="14" t="n">
-        <v>82836</v>
+        <v>81951</v>
       </c>
       <c r="G10" s="14" t="n">
-        <v>383642</v>
+        <v>382795</v>
       </c>
     </row>
     <row r="11" ht="18" customHeight="1">
@@ -2313,7 +2313,7 @@
         </is>
       </c>
       <c r="F11" s="13" t="n">
-        <v>84075634</v>
+        <v>86719924</v>
       </c>
       <c r="G11" s="13" t="n"/>
     </row>
@@ -2344,7 +2344,7 @@
         </is>
       </c>
       <c r="F12" s="13" t="n">
-        <v>82176294</v>
+        <v>82986819</v>
       </c>
       <c r="G12" s="13" t="n"/>
     </row>
@@ -2375,10 +2375,10 @@
         </is>
       </c>
       <c r="F13" s="14" t="n">
-        <v>4633140</v>
+        <v>4638632</v>
       </c>
       <c r="G13" s="14" t="n">
-        <v>21552393</v>
+        <v>21500752</v>
       </c>
     </row>
     <row r="14" ht="20.25" customHeight="1">
@@ -2408,10 +2408,10 @@
         </is>
       </c>
       <c r="F14" s="14" t="n">
-        <v>359921</v>
+        <v>361637</v>
       </c>
       <c r="G14" s="14" t="n">
-        <v>1675977</v>
+        <v>1672872</v>
       </c>
     </row>
     <row r="15" ht="18" customHeight="1">
@@ -2441,10 +2441,10 @@
         </is>
       </c>
       <c r="F15" s="14" t="n">
-        <v>620121</v>
+        <v>621072</v>
       </c>
       <c r="G15" s="14" t="n">
-        <v>2876037</v>
+        <v>2869888</v>
       </c>
     </row>
     <row r="16" ht="18" customHeight="1">
@@ -2474,10 +2474,10 @@
         </is>
       </c>
       <c r="F16" s="14" t="n">
-        <v>73798849</v>
+        <v>74598398</v>
       </c>
       <c r="G16" s="14" t="n">
-        <v>344526205</v>
+        <v>344726269</v>
       </c>
     </row>
     <row r="17" ht="18" customHeight="1">
@@ -2507,10 +2507,10 @@
         </is>
       </c>
       <c r="F17" s="14" t="n">
-        <v>1243115</v>
+        <v>1243184</v>
       </c>
       <c r="G17" s="14" t="n">
-        <v>5755052</v>
+        <v>5751551</v>
       </c>
     </row>
     <row r="18" ht="18" customHeight="1">
@@ -2540,10 +2540,10 @@
         </is>
       </c>
       <c r="F18" s="14" t="n">
-        <v>409531</v>
+        <v>413933</v>
       </c>
       <c r="G18" s="14" t="n">
-        <v>1913530</v>
+        <v>1919013</v>
       </c>
     </row>
     <row r="19" ht="18" customHeight="1">
@@ -2573,10 +2573,10 @@
         </is>
       </c>
       <c r="F19" s="14" t="n">
-        <v>2071432</v>
+        <v>2065651</v>
       </c>
       <c r="G19" s="14" t="n">
-        <v>9591548</v>
+        <v>9601564</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1">
@@ -2606,10 +2606,10 @@
         </is>
       </c>
       <c r="F20" s="14" t="n">
-        <v>512693</v>
+        <v>515161</v>
       </c>
       <c r="G20" s="14" t="n">
-        <v>2392641</v>
+        <v>2401065</v>
       </c>
     </row>
     <row r="21" ht="18" customHeight="1">
@@ -2639,10 +2639,10 @@
         </is>
       </c>
       <c r="F21" s="14" t="n">
-        <v>1859380</v>
+        <v>1849973</v>
       </c>
       <c r="G21" s="14" t="n">
-        <v>8627637</v>
+        <v>8642427</v>
       </c>
     </row>
     <row r="22" ht="18" customHeight="1">
@@ -2672,10 +2672,10 @@
         </is>
       </c>
       <c r="F22" s="14" t="n">
-        <v>39960</v>
+        <v>39829</v>
       </c>
       <c r="G22" s="14" t="n">
-        <v>199952</v>
+        <v>200391</v>
       </c>
     </row>
     <row r="23" ht="18" customHeight="1">
@@ -2705,10 +2705,10 @@
         </is>
       </c>
       <c r="F23" s="14" t="n">
-        <v>0</v>
+        <v>1106142</v>
       </c>
       <c r="G23" s="14" t="n">
-        <v>0</v>
+        <v>5177822</v>
       </c>
     </row>
     <row r="24" ht="18" customHeight="1">
@@ -2738,10 +2738,10 @@
         </is>
       </c>
       <c r="F24" s="14" t="n">
-        <v>0</v>
+        <v>737161</v>
       </c>
       <c r="G24" s="14" t="n">
-        <v>0</v>
+        <v>3448251</v>
       </c>
     </row>
     <row r="25" ht="18" customHeight="1">
@@ -2771,7 +2771,7 @@
         </is>
       </c>
       <c r="F25" s="13" t="n">
-        <v>55857608</v>
+        <v>60068388</v>
       </c>
       <c r="G25" s="13" t="n"/>
     </row>
@@ -2802,7 +2802,7 @@
         </is>
       </c>
       <c r="F26" s="13" t="n">
-        <v>50076029</v>
+        <v>50298844</v>
       </c>
       <c r="G26" s="13" t="n"/>
     </row>
@@ -2833,10 +2833,10 @@
         </is>
       </c>
       <c r="F27" s="14" t="n">
-        <v>49143699</v>
+        <v>49370809</v>
       </c>
       <c r="G27" s="14" t="n">
-        <v>229624369</v>
+        <v>229353427</v>
       </c>
     </row>
     <row r="28" ht="18" customHeight="1">
@@ -2866,10 +2866,10 @@
         </is>
       </c>
       <c r="F28" s="14" t="n">
-        <v>932330</v>
+        <v>928035</v>
       </c>
       <c r="G28" s="14" t="n">
-        <v>4316368</v>
+        <v>4300245</v>
       </c>
     </row>
     <row r="29" ht="18" customHeight="1">
@@ -2899,10 +2899,10 @@
         </is>
       </c>
       <c r="F29" s="14" t="n">
-        <v>0</v>
+        <v>1860371</v>
       </c>
       <c r="G29" s="14" t="n">
-        <v>0</v>
+        <v>8604012</v>
       </c>
     </row>
     <row r="30" ht="18" customHeight="1">
@@ -2932,10 +2932,10 @@
         </is>
       </c>
       <c r="F30" s="14" t="n">
-        <v>0</v>
+        <v>596336</v>
       </c>
       <c r="G30" s="14" t="n">
-        <v>0</v>
+        <v>2755423</v>
       </c>
     </row>
     <row r="31" ht="18" customHeight="1">
@@ -2965,10 +2965,10 @@
         </is>
       </c>
       <c r="F31" s="14" t="n">
-        <v>0</v>
+        <v>373010</v>
       </c>
       <c r="G31" s="14" t="n">
-        <v>0</v>
+        <v>1723875</v>
       </c>
     </row>
     <row r="32" ht="18" customHeight="1">
@@ -2998,10 +2998,10 @@
         </is>
       </c>
       <c r="F32" s="14" t="n">
-        <v>0</v>
+        <v>447505</v>
       </c>
       <c r="G32" s="14" t="n">
-        <v>0</v>
+        <v>2070842</v>
       </c>
     </row>
     <row r="33" ht="18" customHeight="1">
@@ -3031,10 +3031,10 @@
         </is>
       </c>
       <c r="F33" s="14" t="n">
-        <v>0</v>
+        <v>335213</v>
       </c>
       <c r="G33" s="14" t="n">
-        <v>0</v>
+        <v>1554571</v>
       </c>
     </row>
     <row r="34" ht="18" customHeight="1">
@@ -3064,10 +3064,10 @@
         </is>
       </c>
       <c r="F34" s="14" t="n">
-        <v>0</v>
+        <v>223023</v>
       </c>
       <c r="G34" s="14" t="n">
-        <v>0</v>
+        <v>1037034</v>
       </c>
     </row>
     <row r="35" ht="18" customHeight="1">
@@ -3097,10 +3097,10 @@
         </is>
       </c>
       <c r="F35" s="14" t="n">
-        <v>0</v>
+        <v>185396</v>
       </c>
       <c r="G35" s="14" t="n">
-        <v>0</v>
+        <v>864388</v>
       </c>
     </row>
     <row r="36" ht="18" customHeight="1">
@@ -3130,10 +3130,10 @@
         </is>
       </c>
       <c r="F36" s="14" t="n">
-        <v>870304</v>
+        <v>873326</v>
       </c>
       <c r="G36" s="14" t="n">
-        <v>4066330</v>
+        <v>4080922</v>
       </c>
     </row>
     <row r="37" ht="18" customHeight="1">
@@ -3163,10 +3163,10 @@
         </is>
       </c>
       <c r="F37" s="14" t="n">
-        <v>673445</v>
+        <v>666484</v>
       </c>
       <c r="G37" s="14" t="n">
-        <v>3117462</v>
+        <v>3118744</v>
       </c>
     </row>
     <row r="38" ht="18" customHeight="1">
@@ -3196,10 +3196,10 @@
         </is>
       </c>
       <c r="F38" s="14" t="n">
-        <v>512331</v>
+        <v>512047</v>
       </c>
       <c r="G38" s="14" t="n">
-        <v>2392291</v>
+        <v>2396816</v>
       </c>
     </row>
     <row r="39" ht="18" customHeight="1">
@@ -3229,10 +3229,10 @@
         </is>
       </c>
       <c r="F39" s="14" t="n">
-        <v>3929212</v>
+        <v>3890696</v>
       </c>
       <c r="G39" s="14" t="n">
-        <v>18217679</v>
+        <v>18196514</v>
       </c>
     </row>
     <row r="40" ht="18" customHeight="1">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="F40" s="14" t="n">
-        <v>149677</v>
+        <v>153708</v>
       </c>
       <c r="G40" s="14" t="n">
-        <v>749653</v>
+        <v>717559</v>
       </c>
     </row>
     <row r="41" ht="18" customHeight="1">
@@ -3295,10 +3295,10 @@
         </is>
       </c>
       <c r="F41" s="14" t="n">
-        <v>320055</v>
+        <v>318913</v>
       </c>
       <c r="G41" s="14" t="n">
-        <v>1600111</v>
+        <v>1597009</v>
       </c>
     </row>
     <row r="42" ht="18" customHeight="1">
@@ -3328,10 +3328,10 @@
         </is>
       </c>
       <c r="F42" s="14" t="n">
-        <v>360657</v>
+        <v>318913</v>
       </c>
       <c r="G42" s="14" t="n">
-        <v>1800595</v>
+        <v>1597009</v>
       </c>
     </row>
     <row r="43" ht="18" customHeight="1">
@@ -3361,10 +3361,10 @@
         </is>
       </c>
       <c r="F43" s="14" t="n">
-        <v>39855</v>
+        <v>40058</v>
       </c>
       <c r="G43" s="14" t="n">
-        <v>199861</v>
+        <v>199506</v>
       </c>
     </row>
     <row r="44" ht="18" customHeight="1">
@@ -3394,10 +3394,10 @@
         </is>
       </c>
       <c r="F44" s="14" t="n">
-        <v>0</v>
+        <v>162601</v>
       </c>
       <c r="G44" s="14" t="n">
-        <v>0</v>
+        <v>808269</v>
       </c>
     </row>
     <row r="45" ht="18" customHeight="1">
@@ -3427,10 +3427,10 @@
         </is>
       </c>
       <c r="F45" s="14" t="n">
-        <v>0</v>
+        <v>326175</v>
       </c>
       <c r="G45" s="14" t="n">
-        <v>0</v>
+        <v>1507060</v>
       </c>
     </row>
     <row r="46" ht="18" customHeight="1">
@@ -3460,10 +3460,10 @@
         </is>
       </c>
       <c r="F46" s="14" t="n">
-        <v>0</v>
+        <v>108647</v>
       </c>
       <c r="G46" s="14" t="n">
-        <v>0</v>
+        <v>539757</v>
       </c>
     </row>
     <row r="47" ht="18" customHeight="1">
@@ -3493,10 +3493,10 @@
         </is>
       </c>
       <c r="F47" s="14" t="n">
-        <v>0</v>
+        <v>81454</v>
       </c>
       <c r="G47" s="14" t="n">
-        <v>0</v>
+        <v>405240</v>
       </c>
     </row>
     <row r="48" ht="18" customHeight="1">
@@ -3526,10 +3526,10 @@
         </is>
       </c>
       <c r="F48" s="14" t="n">
-        <v>0</v>
+        <v>135573</v>
       </c>
       <c r="G48" s="14" t="n">
-        <v>0</v>
+        <v>676037</v>
       </c>
     </row>
     <row r="49" ht="18" customHeight="1">
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="F49" s="14" t="n">
-        <v>0</v>
+        <v>464486</v>
       </c>
       <c r="G49" s="14" t="n">
-        <v>0</v>
+        <v>2160604</v>
       </c>
     </row>
     <row r="50" ht="18" customHeight="1">
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="F50" s="14" t="n">
-        <v>0</v>
+        <v>71974</v>
       </c>
       <c r="G50" s="14" t="n">
-        <v>0</v>
+        <v>360896</v>
       </c>
     </row>
     <row r="51" ht="18" customHeight="1">
@@ -3625,10 +3625,10 @@
         </is>
       </c>
       <c r="F51" s="14" t="n">
-        <v>0</v>
+        <v>53850</v>
       </c>
       <c r="G51" s="14" t="n">
-        <v>0</v>
+        <v>270630</v>
       </c>
     </row>
     <row r="52" ht="18" customHeight="1">
@@ -3658,10 +3658,10 @@
         </is>
       </c>
       <c r="F52" s="14" t="n">
-        <v>0</v>
+        <v>89575</v>
       </c>
       <c r="G52" s="14" t="n">
-        <v>0</v>
+        <v>450796</v>
       </c>
     </row>
     <row r="53" ht="18" customHeight="1">
@@ -3691,10 +3691,10 @@
         </is>
       </c>
       <c r="F53" s="14" t="n">
-        <v>0</v>
+        <v>62633</v>
       </c>
       <c r="G53" s="14" t="n">
-        <v>0</v>
+        <v>315281</v>
       </c>
     </row>
     <row r="54" ht="18" customHeight="1">
@@ -3724,10 +3724,10 @@
         </is>
       </c>
       <c r="F54" s="14" t="n">
-        <v>0</v>
+        <v>44734</v>
       </c>
       <c r="G54" s="14" t="n">
-        <v>0</v>
+        <v>224968</v>
       </c>
     </row>
     <row r="55" ht="18" customHeight="1">
@@ -3757,10 +3757,10 @@
         </is>
       </c>
       <c r="F55" s="14" t="n">
-        <v>0</v>
+        <v>35822</v>
       </c>
       <c r="G55" s="14" t="n">
-        <v>0</v>
+        <v>179792</v>
       </c>
     </row>
     <row r="56" ht="18" customHeight="1">
@@ -3790,10 +3790,10 @@
         </is>
       </c>
       <c r="F56" s="14" t="n">
-        <v>0</v>
+        <v>26916</v>
       </c>
       <c r="G56" s="14" t="n">
-        <v>0</v>
+        <v>134736</v>
       </c>
     </row>
     <row r="57" ht="18" customHeight="1">
@@ -3823,7 +3823,7 @@
         </is>
       </c>
       <c r="F57" s="13" t="n">
-        <v>28218026</v>
+        <v>27784140</v>
       </c>
       <c r="G57" s="13" t="n"/>
     </row>
@@ -3854,7 +3854,7 @@
         </is>
       </c>
       <c r="F58" s="13" t="n">
-        <v>32399110</v>
+        <v>30811804</v>
       </c>
       <c r="G58" s="13" t="n"/>
     </row>
@@ -3885,10 +3885,10 @@
         </is>
       </c>
       <c r="F59" s="14" t="n">
-        <v>0</v>
+        <v>186135</v>
       </c>
       <c r="G59" s="14" t="n">
-        <v>0</v>
+        <v>860552</v>
       </c>
     </row>
     <row r="60" ht="18" customHeight="1">
@@ -3918,10 +3918,10 @@
         </is>
       </c>
       <c r="F60" s="14" t="n">
-        <v>0</v>
+        <v>45246</v>
       </c>
       <c r="G60" s="14" t="n">
-        <v>0</v>
+        <v>224707</v>
       </c>
     </row>
     <row r="61" ht="18" customHeight="1">
@@ -3951,10 +3951,10 @@
         </is>
       </c>
       <c r="F61" s="14" t="n">
-        <v>69818</v>
+        <v>70420</v>
       </c>
       <c r="G61" s="14" t="n">
-        <v>349830</v>
+        <v>349890</v>
       </c>
     </row>
     <row r="62" ht="18" customHeight="1">
@@ -3984,7 +3984,7 @@
         </is>
       </c>
       <c r="F62" s="13" t="n">
-        <v>28148208</v>
+        <v>27899855</v>
       </c>
       <c r="G62" s="13" t="n"/>
     </row>
@@ -4015,10 +4015,10 @@
         </is>
       </c>
       <c r="F63" s="14" t="n">
-        <v>2486477</v>
+        <v>2509989</v>
       </c>
       <c r="G63" s="14" t="n">
-        <v>12486683</v>
+        <v>12520553</v>
       </c>
     </row>
     <row r="64" ht="18" customHeight="1">
@@ -4048,7 +4048,7 @@
         </is>
       </c>
       <c r="F64" s="13" t="n">
-        <v>25661731</v>
+        <v>25389866</v>
       </c>
       <c r="G64" s="13" t="n"/>
     </row>
@@ -4108,7 +4108,7 @@
         </is>
       </c>
       <c r="F66" s="13" t="n">
-        <v>25661731</v>
+        <v>25389866</v>
       </c>
       <c r="G66" s="13" t="n"/>
     </row>
@@ -4201,7 +4201,7 @@
         </is>
       </c>
       <c r="F69" s="13" t="n">
-        <v>25661731</v>
+        <v>25389866</v>
       </c>
       <c r="G69" s="13" t="n"/>
     </row>
@@ -4410,7 +4410,7 @@
         </is>
       </c>
       <c r="F76" s="13" t="n">
-        <v>25661731</v>
+        <v>25389866</v>
       </c>
       <c r="G76" s="13" t="n"/>
     </row>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="F77" s="13" t="n">
-        <v>25661731</v>
+        <v>25389866</v>
       </c>
       <c r="G77" s="13" t="n"/>
     </row>
